--- a/Pruebas/19 OCTUBRE MERCADO.xlsx
+++ b/Pruebas/19 OCTUBRE MERCADO.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7125"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7125"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -323,16 +323,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -623,16 +631,16 @@
   <dimension ref="A1:S344"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="8" customWidth="1"/>
+    <col min="16" max="16" width="23.28515625" customWidth="1"/>
+    <col min="19" max="19" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1">
+      <c r="A1" s="8">
         <v>45700063898</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -645,12 +653,12 @@
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="9" t="s">
         <v>49</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="9" t="s">
         <v>50</v>
       </c>
       <c r="N1" s="1"/>
@@ -665,236 +673,236 @@
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="4">
         <v>45699493978</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="10">
         <v>45705129646</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="8">
         <v>45684164331</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="5">
         <v>45702368307</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="6">
         <v>45704475024</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <v>45699243529</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="10">
         <v>45689034640</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="8">
         <v>45684164441</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="5">
         <v>45703326317</v>
       </c>
-      <c r="S3" s="7">
+      <c r="S3" s="6">
         <v>45693698304</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>45699242131</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="10">
         <v>45697469810</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="8">
         <v>45699514963</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="5">
         <v>45700079680</v>
       </c>
-      <c r="S4" s="7">
+      <c r="S4" s="6">
         <v>45699071106</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="8">
         <v>45704777040</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="4">
         <v>45699494496</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="8">
         <v>45699605799</v>
       </c>
-      <c r="P5" s="6">
+      <c r="P5" s="5">
         <v>45700079680</v>
       </c>
-      <c r="S5" s="8">
+      <c r="S5" s="7">
         <v>45697611806</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="4">
         <v>45699494110</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="10">
         <v>45699881954</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="8">
         <v>45702928108</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="5">
         <v>45691751803</v>
       </c>
-      <c r="S6" s="8">
+      <c r="S6" s="7">
         <v>45699798530</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="8">
         <v>45697121539</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <v>45699244207</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="10">
         <v>45693171293</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="8">
         <v>45704045288</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="5">
         <v>45702040031</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="7">
         <v>45697611826</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="8">
         <v>45702761907</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="4">
         <v>45699242637</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="8">
         <v>45701549945</v>
       </c>
-      <c r="P8" s="6">
+      <c r="P8" s="5">
         <v>45699939976</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="7">
         <v>45699689385</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="8">
         <v>45699885320</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="4">
         <v>45699242423</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="10">
         <v>45701093483</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="8">
         <v>45701550089</v>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="5">
         <v>45698480650</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="7">
         <v>45689123174</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="8">
         <v>45705129646</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>45699242179</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="10">
         <v>45703433836</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="8">
         <v>45690285008</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="5">
         <v>45699830331</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="7">
         <v>45698819773</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="4">
         <v>45699493940</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="8">
         <v>45704103195</v>
       </c>
-      <c r="P11" s="6">
+      <c r="P11" s="5">
         <v>45697034209</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="7">
         <v>45701236513</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="A12" s="8">
         <v>45695955617</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <v>45699242109</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="8">
         <v>45703793607</v>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="5">
         <v>45701894220</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="7">
         <v>45690629541</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="A13" s="8">
         <v>45692888932</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="4">
         <v>45699242009</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="10">
         <v>45696044459</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="8">
         <v>45704044978</v>
       </c>
-      <c r="P13" s="6">
+      <c r="P13" s="5">
         <v>45698155880</v>
       </c>
       <c r="S13">
@@ -902,16 +910,16 @@
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="A14" s="8">
         <v>45697281720</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="4">
         <v>45699243665</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="P14" s="6" t="s">
+      <c r="P14" s="5" t="s">
         <v>58</v>
       </c>
       <c r="S14">
@@ -919,19 +927,19 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" s="8">
         <v>45699493846</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="4">
         <v>45699493340</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="8">
         <v>45649851963</v>
       </c>
-      <c r="P15" s="6">
+      <c r="P15" s="5">
         <v>45683776687</v>
       </c>
       <c r="S15">
@@ -939,19 +947,19 @@
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="A16" s="8">
         <v>45699494416</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="4">
         <v>45699494048</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="10">
         <v>45705052898</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="8">
         <v>45690195584</v>
       </c>
-      <c r="P16" s="6">
+      <c r="P16" s="5">
         <v>45702029280</v>
       </c>
       <c r="S16">
@@ -959,358 +967,358 @@
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="A17" s="8">
         <v>45699494068</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="4">
         <v>45699493916</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="10">
         <v>45699840900</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="8">
         <v>45689945617</v>
       </c>
-      <c r="P17" s="6">
+      <c r="P17" s="5">
         <v>45702368435</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="8">
         <v>45699242141</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <v>45699242485</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="8">
         <v>45690297297</v>
       </c>
-      <c r="P18" s="6">
+      <c r="P18" s="5">
         <v>45704803084</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="A19" s="8">
         <v>45699493296</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="4">
         <v>45699493826</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="8">
         <v>45702423555</v>
       </c>
-      <c r="P19" s="6">
+      <c r="P19" s="5">
         <v>45698626279</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="A20" s="8">
         <v>45699494198</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="4">
         <v>45699242513</v>
       </c>
-      <c r="J20" s="4">
+      <c r="J20" s="10">
         <v>45690155264</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="8">
         <v>45691369114</v>
       </c>
-      <c r="P20" s="6" t="s">
+      <c r="P20" s="5" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="A21" s="8">
         <v>45699242741</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="4">
         <v>45699493970</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="8">
         <v>45699886090</v>
       </c>
-      <c r="P21" s="6">
+      <c r="P21" s="5">
         <v>45693231467</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="A22" s="8">
         <v>45699242513</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="4">
         <v>45699242621</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="8">
         <v>45699288437</v>
       </c>
-      <c r="P22" s="6">
+      <c r="P22" s="5">
         <v>45700230387</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="A23" s="8">
         <v>45704653552</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="4">
         <v>45699242141</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="8">
         <v>45703969703</v>
       </c>
-      <c r="P23" s="6">
+      <c r="P23" s="5">
         <v>45697837141</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="A24" s="8">
         <v>45695619493</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="4">
         <v>45699242741</v>
       </c>
-      <c r="J24" s="4">
+      <c r="J24" s="10">
         <v>45699422202</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="8">
         <v>45699867991</v>
       </c>
-      <c r="P24" s="6">
+      <c r="P24" s="5">
         <v>45691749133</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="A25" s="8">
         <v>45703786720</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="4">
         <v>45699494198</v>
       </c>
-      <c r="J25" s="4">
+      <c r="J25" s="10">
         <v>45705002132</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="8">
         <v>45702954173</v>
       </c>
-      <c r="P25" s="6">
+      <c r="P25" s="5">
         <v>45702580380</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="A26" s="8">
         <v>45702322569</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="4">
         <v>45699493296</v>
       </c>
-      <c r="J26" s="4">
+      <c r="J26" s="10">
         <v>45695035519</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="8">
         <v>45703601886</v>
       </c>
-      <c r="P26" s="6">
+      <c r="P26" s="5">
         <v>45697837113</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="A27" s="8">
         <v>45699973489</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="4">
         <v>45699494416</v>
       </c>
-      <c r="J27" s="4" t="s">
+      <c r="J27" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="8">
         <v>45689945453</v>
       </c>
-      <c r="P27" s="6" t="s">
+      <c r="P27" s="5" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="A28" s="8">
         <v>45703348097</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="4">
         <v>45699494068</v>
       </c>
-      <c r="J28" s="4">
+      <c r="J28" s="10">
         <v>45698509391</v>
       </c>
-      <c r="M28" t="s">
+      <c r="M28" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="P28" s="6">
+      <c r="P28" s="5">
         <v>45697987915</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="A29" s="8">
         <v>45702126572</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="4">
         <v>45699493846</v>
       </c>
-      <c r="J29" s="4">
+      <c r="J29" s="10">
         <v>45703786720</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="8">
         <v>45702423673</v>
       </c>
-      <c r="P29" s="6">
+      <c r="P29" s="5">
         <v>45689726417</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="A30" s="8">
         <v>45699567167</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="4">
         <v>45705172784</v>
       </c>
-      <c r="J30" s="4">
+      <c r="J30" s="10">
         <v>45703534155</v>
       </c>
-      <c r="M30">
+      <c r="M30" s="8">
         <v>45699109430</v>
       </c>
-      <c r="P30" s="6">
+      <c r="P30" s="5">
         <v>45701966115</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="A31" s="8">
         <v>45700933640</v>
       </c>
-      <c r="J31" s="4">
+      <c r="J31" s="10">
         <v>45699653891</v>
       </c>
-      <c r="M31">
+      <c r="M31" s="8">
         <v>45693400607</v>
       </c>
-      <c r="P31" s="6">
+      <c r="P31" s="5">
         <v>45699732877</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="M32">
+      <c r="M32" s="8">
         <v>45698294598</v>
       </c>
-      <c r="P32" s="6">
+      <c r="P32" s="5">
         <v>45703154739</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="A33" s="8">
         <v>45690297297</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="4">
         <v>45692890232</v>
       </c>
-      <c r="J33" s="4">
+      <c r="J33" s="10">
         <v>957075870015</v>
       </c>
-      <c r="M33">
+      <c r="M33" s="8">
         <v>954893920015</v>
       </c>
-      <c r="P33" s="6" t="s">
+      <c r="P33" s="5" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="A34" s="8">
         <v>45699791173</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="4">
         <v>45692888932</v>
       </c>
-      <c r="J34" s="4">
+      <c r="J34" s="10">
         <v>45699567167</v>
       </c>
-      <c r="M34">
+      <c r="M34" s="8">
         <v>45689945681</v>
       </c>
-      <c r="P34" s="6">
+      <c r="P34" s="5">
         <v>45702029296</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="A35" s="8">
         <v>45701549945</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="4">
         <v>45702095740</v>
       </c>
-      <c r="J35" s="4">
+      <c r="J35" s="10">
         <v>45701212869</v>
       </c>
-      <c r="M35">
+      <c r="M35" s="8">
         <v>45693076279</v>
       </c>
-      <c r="P35" s="6">
+      <c r="P35" s="5">
         <v>45695319715</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="A36" s="8">
         <v>45704042178</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="4">
         <v>45704147731</v>
       </c>
-      <c r="J36" s="4">
+      <c r="J36" s="10">
         <v>45704260229</v>
       </c>
-      <c r="M36">
+      <c r="M36" s="8">
         <v>45692899357</v>
       </c>
-      <c r="P36" s="6">
+      <c r="P36" s="5">
         <v>45678733429</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37">
+      <c r="A37" s="8">
         <v>45697987915</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="4">
         <v>45698836573</v>
       </c>
-      <c r="J37" s="4">
+      <c r="J37" s="10">
         <v>45696962872</v>
       </c>
-      <c r="M37" t="s">
+      <c r="M37" s="8" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38">
+      <c r="A38" s="8">
         <v>45704803084</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="4">
         <v>45697827306</v>
       </c>
-      <c r="J38" s="4">
+      <c r="J38" s="10">
         <v>45696368882</v>
       </c>
-      <c r="M38" t="s">
+      <c r="M38" s="8" t="s">
         <v>53</v>
       </c>
       <c r="P38" s="3">
@@ -1318,16 +1326,16 @@
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39">
+      <c r="A39" s="8">
         <v>45699676306</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="4">
         <v>45700196386</v>
       </c>
-      <c r="J39" s="4">
+      <c r="J39" s="10">
         <v>45702687699</v>
       </c>
-      <c r="M39">
+      <c r="M39" s="8">
         <v>45697825672</v>
       </c>
       <c r="P39" s="3">
@@ -1335,16 +1343,16 @@
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40">
+      <c r="A40" s="8">
         <v>45701687998</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="4">
         <v>957200080019</v>
       </c>
-      <c r="J40" s="4">
+      <c r="J40" s="10">
         <v>957075880014</v>
       </c>
-      <c r="M40">
+      <c r="M40" s="8">
         <v>45694062549</v>
       </c>
       <c r="P40" s="3">
@@ -1352,1897 +1360,1897 @@
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41">
+      <c r="A41" s="8">
         <v>45697084294</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="4">
         <v>45699919276</v>
       </c>
-      <c r="J41" s="4">
+      <c r="J41" s="10">
         <v>45688721304</v>
       </c>
-      <c r="M41">
+      <c r="M41" s="8">
         <v>45697673787</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42">
+      <c r="A42" s="8">
         <v>45693268355</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="4">
         <v>45704399580</v>
       </c>
-      <c r="J42" s="4">
+      <c r="J42" s="10">
         <v>45699677861</v>
       </c>
-      <c r="M42">
+      <c r="M42" s="8">
         <v>45693212589</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="4">
         <v>45699415021</v>
       </c>
-      <c r="J43" s="4">
+      <c r="J43" s="10">
         <v>45704050451</v>
       </c>
-      <c r="M43">
+      <c r="M43" s="8">
         <v>956631860015</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44">
+      <c r="A44" s="8">
         <v>45700182914</v>
       </c>
-      <c r="J44" s="4">
+      <c r="J44" s="10">
         <v>45696423731</v>
       </c>
-      <c r="M44" t="s">
+      <c r="M44" s="8" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45">
+      <c r="A45" s="8">
         <v>45703420443</v>
       </c>
       <c r="G45" s="3">
         <v>45697894496</v>
       </c>
-      <c r="J45" s="4">
+      <c r="J45" s="10">
         <v>45695003918</v>
       </c>
-      <c r="M45">
+      <c r="M45" s="8">
         <v>45696698018</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46">
+      <c r="A46" s="8">
         <v>45700230387</v>
       </c>
       <c r="G46" s="3">
         <v>45697643785</v>
       </c>
-      <c r="J46" s="4">
+      <c r="J46" s="10">
         <v>45704239223</v>
       </c>
-      <c r="M46">
+      <c r="M46" s="8">
         <v>45696975144</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47">
+      <c r="A47" s="8">
         <v>45699867991</v>
       </c>
       <c r="G47" s="3">
         <v>45704229284</v>
       </c>
-      <c r="J47" s="4">
+      <c r="J47" s="10">
         <v>45699818000</v>
       </c>
-      <c r="M47">
+      <c r="M47" s="8">
         <v>45696975118</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48">
+      <c r="A48" s="8">
         <v>45699873149</v>
       </c>
       <c r="G48" s="3">
         <v>45697895010</v>
       </c>
-      <c r="J48" s="4">
+      <c r="J48" s="10">
         <v>45700103544</v>
       </c>
-      <c r="M48">
+      <c r="M48" s="8">
         <v>954875830018</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49">
+      <c r="A49" s="8">
         <v>45699425359</v>
       </c>
       <c r="G49" s="3">
         <v>45696000795</v>
       </c>
-      <c r="J49" s="4">
+      <c r="J49" s="10">
         <v>45695955617</v>
       </c>
-      <c r="M49">
+      <c r="M49" s="8">
         <v>45704198992</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50">
+      <c r="A50" s="8">
         <v>45698881742</v>
       </c>
       <c r="G50" s="3">
         <v>45703892379</v>
       </c>
-      <c r="J50" s="4">
+      <c r="J50" s="10">
         <v>45699062690</v>
       </c>
-      <c r="M50">
+      <c r="M50" s="8">
         <v>45688749531</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51">
+      <c r="A51" s="8">
         <v>45696927564</v>
       </c>
       <c r="G51" s="3">
         <v>45682044633</v>
       </c>
-      <c r="J51" s="4">
+      <c r="J51" s="10">
         <v>45700182914</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52">
+      <c r="A52" s="8">
         <v>45702499352</v>
       </c>
       <c r="G52" s="3">
         <v>954532130018</v>
       </c>
-      <c r="M52">
+      <c r="M52" s="8">
         <v>45704550535</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" s="8" t="s">
         <v>7</v>
       </c>
       <c r="G53" s="3">
         <v>957295300017</v>
       </c>
-      <c r="J53" s="4">
+      <c r="J53" s="10">
         <v>45699812543</v>
       </c>
-      <c r="M53" t="s">
+      <c r="M53" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54">
+      <c r="A54" s="8">
         <v>45696446653</v>
       </c>
       <c r="G54" s="3">
         <v>45701687998</v>
       </c>
-      <c r="J54" s="4">
+      <c r="J54" s="10">
         <v>45700063174</v>
       </c>
-      <c r="M54">
+      <c r="M54" s="8">
         <v>45703420443</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A55">
+      <c r="A55" s="8">
         <v>45700103544</v>
       </c>
       <c r="G55" s="3">
         <v>45693563299</v>
       </c>
-      <c r="J55" s="4">
+      <c r="J55" s="10">
         <v>45700063898</v>
       </c>
-      <c r="M55">
+      <c r="M55" s="8">
         <v>45703466941</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A56">
+      <c r="A56" s="8">
         <v>45704227799</v>
       </c>
       <c r="G56" s="3">
         <v>45699739654</v>
       </c>
-      <c r="J56" s="4">
+      <c r="J56" s="10">
         <v>45700063180</v>
       </c>
-      <c r="M56">
+      <c r="M56" s="8">
         <v>45703582771</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A57">
+      <c r="A57" s="8">
         <v>45702368435</v>
       </c>
       <c r="G57" s="3">
         <v>45700933640</v>
       </c>
-      <c r="J57" s="4">
+      <c r="J57" s="10">
         <v>45700063198</v>
       </c>
-      <c r="M57">
+      <c r="M57" s="8">
         <v>45693246113</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A58">
+      <c r="A58" s="8">
         <v>45699556805</v>
       </c>
       <c r="G58" s="3">
         <v>45701125466</v>
       </c>
-      <c r="J58" s="4">
+      <c r="J58" s="10">
         <v>45693761264</v>
       </c>
-      <c r="M58">
+      <c r="M58" s="8">
         <v>45684724883</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A59">
+      <c r="A59" s="8">
         <v>45676144045</v>
       </c>
       <c r="G59" s="3">
         <v>45698983373</v>
       </c>
-      <c r="J59" s="4">
+      <c r="J59" s="10">
         <v>45697281720</v>
       </c>
-      <c r="M59">
+      <c r="M59" s="8">
         <v>45703348097</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A60">
+      <c r="A60" s="8">
         <v>45703466941</v>
       </c>
       <c r="G60" s="3">
         <v>45704459557</v>
       </c>
-      <c r="J60" s="4">
+      <c r="J60" s="10">
         <v>45699505508</v>
       </c>
-      <c r="M60" t="s">
+      <c r="M60" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A61">
+      <c r="A61" s="8">
         <v>45703711142</v>
       </c>
       <c r="G61" s="3">
         <v>45700260742</v>
       </c>
-      <c r="J61" s="4">
+      <c r="J61" s="10">
         <v>45676144045</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A62">
+      <c r="A62" s="8">
         <v>45699514963</v>
       </c>
       <c r="G62" s="3">
         <v>45699791173</v>
       </c>
-      <c r="J62" s="4">
+      <c r="J62" s="10">
         <v>45690351196</v>
       </c>
-      <c r="M62">
+      <c r="M62" s="8">
         <v>45678148933</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A63">
+      <c r="A63" s="8">
         <v>45697895010</v>
       </c>
       <c r="G63" s="3">
         <v>45683464616</v>
       </c>
-      <c r="J63" s="4">
+      <c r="J63" s="10">
         <v>45704062347</v>
       </c>
-      <c r="M63" t="s">
+      <c r="M63" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A64">
+      <c r="A64" s="8">
         <v>45681464627</v>
       </c>
       <c r="G64" s="3">
         <v>45701310033</v>
       </c>
-      <c r="J64" s="4">
+      <c r="J64" s="10">
         <v>45702340133</v>
       </c>
-      <c r="M64">
+      <c r="M64" s="8">
         <v>45704623911</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65">
+      <c r="A65" s="8">
         <v>45703288602</v>
       </c>
       <c r="G65" s="3">
         <v>45693298428</v>
       </c>
-      <c r="J65" s="4">
+      <c r="J65" s="10">
         <v>45703533780</v>
       </c>
-      <c r="M65">
+      <c r="M65" s="8">
         <v>45684408052</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A66">
+      <c r="A66" s="8">
         <v>45703533780</v>
       </c>
       <c r="G66" s="3">
         <v>45697053419</v>
       </c>
-      <c r="J66" s="4">
+      <c r="J66" s="10">
         <v>45705258130</v>
       </c>
-      <c r="M66">
+      <c r="M66" s="8">
         <v>45700467270</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="A67" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G67" s="3">
         <v>45699784957</v>
       </c>
-      <c r="J67" s="4">
+      <c r="J67" s="10">
         <v>45704062357</v>
       </c>
-      <c r="M67">
+      <c r="M67" s="8">
         <v>45692975453</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68">
+      <c r="A68" s="8">
         <v>45699785039</v>
       </c>
       <c r="G68" s="3">
         <v>45701874401</v>
       </c>
-      <c r="J68" s="4">
+      <c r="J68" s="10">
         <v>45705084190</v>
       </c>
-      <c r="M68">
+      <c r="M68" s="8">
         <v>954173470012</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69">
+      <c r="A69" s="8">
         <v>45702340133</v>
       </c>
       <c r="G69" s="3">
         <v>45702126572</v>
       </c>
-      <c r="M69">
+      <c r="M69" s="8">
         <v>45702763080</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A70">
+      <c r="A70" s="8">
         <v>45698819773</v>
       </c>
       <c r="G70" s="3">
         <v>45693268355</v>
       </c>
-      <c r="J70" s="4">
+      <c r="J70" s="10">
         <v>45704479878</v>
       </c>
-      <c r="M70">
+      <c r="M70" s="8">
         <v>45695881096</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A71">
+      <c r="A71" s="8">
         <v>45699505508</v>
       </c>
       <c r="G71" s="3">
         <v>45699785039</v>
       </c>
-      <c r="J71" s="4">
+      <c r="J71" s="10">
         <v>45704227799</v>
       </c>
-      <c r="M71">
+      <c r="M71" s="8">
         <v>957196080015</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A72">
+      <c r="A72" s="8">
         <v>45700063198</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="J72" s="4">
+      <c r="J72" s="10">
         <v>45693810663</v>
       </c>
-      <c r="M72" t="s">
+      <c r="M72" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73">
+      <c r="A73" s="8">
         <v>45705052898</v>
       </c>
       <c r="G73" s="3">
         <v>45700833289</v>
       </c>
-      <c r="J73" s="4">
+      <c r="J73" s="10">
         <v>45704776976</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74">
+      <c r="A74" s="8">
         <v>45699096781</v>
       </c>
       <c r="G74" s="3">
         <v>45698254809</v>
       </c>
-      <c r="J74" s="4">
+      <c r="J74" s="10">
         <v>45704777040</v>
       </c>
-      <c r="M74">
+      <c r="M74" s="8">
         <v>45703969577</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75">
+      <c r="A75" s="8">
         <v>45695881096</v>
       </c>
       <c r="G75" s="3">
         <v>957061410016</v>
       </c>
-      <c r="J75" s="4">
+      <c r="J75" s="10">
         <v>45697084294</v>
       </c>
-      <c r="M75">
+      <c r="M75" s="8">
         <v>45703947219</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76">
+      <c r="A76" s="8">
         <v>45699818000</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J76" s="4">
+      <c r="J76" s="10">
         <v>45703809995</v>
       </c>
-      <c r="M76">
+      <c r="M76" s="8">
         <v>45692887990</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77">
+      <c r="A77" s="8">
         <v>45689945617</v>
       </c>
       <c r="G77" s="3">
         <v>45701875543</v>
       </c>
-      <c r="J77" s="4">
+      <c r="J77" s="10">
         <v>45699217101</v>
       </c>
-      <c r="M77">
+      <c r="M77" s="8">
         <v>45673029741</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78">
+      <c r="A78" s="8">
         <v>45699415021</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J78" s="4">
+      <c r="J78" s="10">
         <v>45701644708</v>
       </c>
-      <c r="M78">
+      <c r="M78" s="8">
         <v>45696446653</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79">
+      <c r="A79" s="8">
         <v>45699288437</v>
       </c>
-      <c r="J79" s="4">
+      <c r="J79" s="10">
         <v>45701643928</v>
       </c>
-      <c r="M79">
+      <c r="M79" s="8">
         <v>45702928214</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80">
+      <c r="A80" s="8">
         <v>45701032924</v>
       </c>
       <c r="G80">
         <v>45704042178</v>
       </c>
-      <c r="M80">
+      <c r="M80" s="8">
         <v>45702928078</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81">
+      <c r="A81" s="8">
         <v>45693563299</v>
       </c>
-      <c r="J81">
+      <c r="J81" s="8">
         <v>45703020197</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82">
+      <c r="A82" s="8">
         <v>45700467270</v>
       </c>
-      <c r="J82">
+      <c r="J82" s="8">
         <v>45703288602</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83">
+      <c r="A83" s="8">
         <v>45704239223</v>
       </c>
-      <c r="J83">
+      <c r="J83" s="8">
         <v>45704816778</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84">
+      <c r="A84" s="8">
         <v>45697611806</v>
       </c>
-      <c r="J84">
+      <c r="J84" s="8">
         <v>45703184035</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85">
+      <c r="A85" s="8">
         <v>45693231467</v>
       </c>
-      <c r="J85">
+      <c r="J85" s="8">
         <v>45686185223</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86">
+      <c r="A86" s="8">
         <v>45697837113</v>
       </c>
-      <c r="J86">
+      <c r="J86" s="8">
         <v>45695780380</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87">
+      <c r="A87" s="8">
         <v>45691749133</v>
       </c>
-      <c r="J87">
+      <c r="J87" s="8">
         <v>45695780182</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88">
+      <c r="A88" s="8">
         <v>45702095740</v>
       </c>
-      <c r="J88" t="s">
+      <c r="J88" s="8" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89">
+      <c r="A89" s="8">
         <v>45704198992</v>
       </c>
-      <c r="J89">
+      <c r="J89" s="8">
         <v>45701032924</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90">
+      <c r="A90" s="8">
         <v>45704550535</v>
       </c>
-      <c r="J90">
+      <c r="J90" s="8">
         <v>45701066338</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91">
+      <c r="A91" s="8">
         <v>45701966115</v>
       </c>
-      <c r="J91">
+      <c r="J91" s="8">
         <v>45701032902</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92">
+      <c r="A92" s="8">
         <v>45700260742</v>
       </c>
-      <c r="J92">
+      <c r="J92" s="8">
         <v>45699706163</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93">
+      <c r="A93" s="8">
         <v>45704062357</v>
       </c>
-      <c r="J93" t="s">
+      <c r="J93" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94">
+      <c r="A94" s="8">
         <v>45701032902</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95">
+      <c r="A95" s="8">
         <v>45701894220</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96">
+      <c r="A96" s="8">
         <v>45703969577</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97">
+      <c r="A97" s="8">
         <v>45704103195</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98">
+      <c r="A98" s="8">
         <v>45705002132</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99">
+      <c r="A99" s="8">
         <v>45702954173</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100">
+      <c r="A100" s="8">
         <v>45703427148</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101">
+      <c r="A101" s="8">
         <v>45699677861</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102">
+      <c r="A102" s="8">
         <v>45704816778</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103">
+      <c r="A103" s="8">
         <v>45702600266</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104">
+      <c r="A104" s="8">
         <v>45700130558</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105">
+      <c r="A105" s="8">
         <v>45678148911</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106">
+      <c r="A106" s="8">
         <v>45703809995</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107">
+      <c r="A107" s="8">
         <v>45700204878</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108">
+      <c r="A108" s="8">
         <v>45698543138</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109">
+      <c r="A109" s="8">
         <v>45701873461</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="A110" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111">
+      <c r="A111" s="8">
         <v>45702928108</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112">
+      <c r="A112" s="8">
         <v>45696423731</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113">
+      <c r="A113" s="8">
         <v>45704399580</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114">
+      <c r="A114" s="8">
         <v>45690304969</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115">
+      <c r="A115" s="8">
         <v>45704229284</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116">
+      <c r="A116" s="8">
         <v>45699784957</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117">
+      <c r="A117" s="8">
         <v>45704479878</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118">
+      <c r="A118" s="8">
         <v>45701125466</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119">
+      <c r="A119" s="8">
         <v>45697643785</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120">
+      <c r="A120" s="8">
         <v>45698836573</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121">
+      <c r="A121" s="8">
         <v>45699732877</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122">
+      <c r="A122" s="8">
         <v>45703582771</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123">
+      <c r="A123" s="8">
         <v>45702029296</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124">
+      <c r="A124" s="8">
         <v>45699217101</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125">
+      <c r="A125" s="8">
         <v>45696962872</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126">
+      <c r="A126" s="8">
         <v>45702042013</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127">
+      <c r="A127" s="8">
         <v>45696000795</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128">
+      <c r="A128" s="8">
         <v>45700131968</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129">
+      <c r="A129" s="8">
         <v>45698155880</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130">
+      <c r="A130" s="8">
         <v>45689123174</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131">
+      <c r="A131" s="8">
         <v>45697053419</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132">
+      <c r="A132" s="8">
         <v>45698626279</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133">
+      <c r="A133" s="8">
         <v>45699542779</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134">
+      <c r="A134" s="8">
         <v>45699689385</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135">
+      <c r="A135" s="8">
         <v>45696368882</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136">
+      <c r="A136" s="8">
         <v>45702763080</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137">
+      <c r="A137" s="8">
         <v>45686581149</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138">
+      <c r="A138" s="8">
         <v>45699886090</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139">
+      <c r="A139" s="8">
         <v>45698983373</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140">
+      <c r="A140" s="8">
         <v>45684164331</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141">
+      <c r="A141" s="8">
         <v>45704050451</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142">
+      <c r="A142" s="8">
         <v>45699739654</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143">
+      <c r="A143" s="8">
         <v>45701874401</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+      <c r="A144" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145">
+      <c r="A145" s="8">
         <v>45703184035</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146">
+      <c r="A146" s="8">
         <v>45697894496</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147">
+      <c r="A147" s="8">
         <v>45699908780</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148">
+      <c r="A148" s="8">
         <v>45699706163</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149">
+      <c r="A149" s="8">
         <v>45682437530</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150">
+      <c r="A150" s="8">
         <v>45697536150</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151">
+      <c r="A151" s="8">
         <v>45705093200</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152">
+      <c r="A152" s="8">
         <v>45699029458</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153">
+      <c r="A153" s="8">
         <v>45699840900</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154">
+      <c r="A154" s="8">
         <v>45703892379</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155">
+      <c r="A155" s="8">
         <v>45701695087</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156">
+      <c r="A156" s="8">
         <v>45695003918</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157">
+      <c r="A157" s="8">
         <v>45699633973</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158">
+      <c r="A158" s="8">
         <v>45704045288</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159">
+      <c r="A159" s="8">
         <v>45701310033</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160">
+      <c r="A160" s="8">
         <v>45702423555</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161">
+      <c r="A161" s="8">
         <v>45701875543</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162">
+      <c r="A162" s="8">
         <v>45699873161</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163">
+      <c r="A163" s="8">
         <v>45686165665</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164">
+      <c r="A164" s="8">
         <v>45695319715</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165">
+      <c r="A165" s="8">
         <v>45700124680</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166">
+      <c r="A166" s="8">
         <v>45697536162</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+      <c r="A167" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168">
+      <c r="A168" s="8">
         <v>45702423673</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169">
+      <c r="A169" s="8">
         <v>45704623911</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170">
+      <c r="A170" s="8">
         <v>45704062347</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171">
+      <c r="A171" s="8">
         <v>45705084190</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+      <c r="A172" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173">
+      <c r="A173" s="8">
         <v>45701650857</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174">
+      <c r="A174" s="8">
         <v>45694898065</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175">
+      <c r="A175" s="8">
         <v>45700063174</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176">
+      <c r="A176" s="8">
         <v>45701644708</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177">
+      <c r="A177" s="8">
         <v>45704147731</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178">
+      <c r="A178" s="8">
         <v>45705259122</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179">
+      <c r="A179" s="8">
         <v>45697022507</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180">
+      <c r="A180" s="8">
         <v>45702467181</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181">
+      <c r="A181" s="8">
         <v>45700063180</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182">
+      <c r="A182" s="8">
         <v>45703947219</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183">
+      <c r="A183" s="8">
         <v>45686846425</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184">
+      <c r="A184" s="8">
         <v>45698885918</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185">
+      <c r="A185" s="8">
         <v>45683359722</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186">
+      <c r="A186" s="8">
         <v>45699605799</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187">
+      <c r="A187" s="8">
         <v>45702470122</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188">
+      <c r="A188" s="8">
         <v>45689726417</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189">
+      <c r="A189" s="8">
         <v>45699919276</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190">
+      <c r="A190" s="8">
         <v>45702687699</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191">
+      <c r="A191" s="8">
         <v>45699422202</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192">
+      <c r="A192" s="8">
         <v>45702573962</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193">
+      <c r="A193" s="8">
         <v>45698509391</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194">
+      <c r="A194" s="8">
         <v>45693698304</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195">
+      <c r="A195" s="8">
         <v>45699798530</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196">
+      <c r="A196" s="8">
         <v>45703154739</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197">
+      <c r="A197" s="8">
         <v>45694245244</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A198">
+      <c r="A198" s="8">
         <v>45698254809</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A199">
+      <c r="A199" s="8">
         <v>45673029741</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A200">
+      <c r="A200" s="8">
         <v>45699939976</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A201">
+      <c r="A201" s="8">
         <v>45699830331</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A202">
+      <c r="A202" s="8">
         <v>45691460604</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A203">
+      <c r="A203" s="8">
         <v>45687646443</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
+      <c r="A204" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A205">
+      <c r="A205" s="8">
         <v>45699109430</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A206">
+      <c r="A206" s="8">
         <v>45703326317</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A207">
+      <c r="A207" s="8">
         <v>45697611826</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A208">
+      <c r="A208" s="8">
         <v>45699242621</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A209">
+      <c r="A209" s="8">
         <v>45705316176</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A210">
+      <c r="A210" s="8">
         <v>45698250950</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A211">
+      <c r="A211" s="8">
         <v>45695035519</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A212">
+      <c r="A212" s="8">
         <v>45699973481</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
+      <c r="A213" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A214">
+      <c r="A214" s="8">
         <v>45693189839</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A215">
+      <c r="A215" s="8">
         <v>45699928643</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A216">
+      <c r="A216" s="8">
         <v>45701093483</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A217">
+      <c r="A217" s="8">
         <v>45704067462</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A218">
+      <c r="A218" s="8">
         <v>45697827306</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A219">
+      <c r="A219" s="8">
         <v>45699742861</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A220">
+      <c r="A220" s="8">
         <v>45682044633</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A221">
+      <c r="A221" s="8">
         <v>45701236513</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A222">
+      <c r="A222" s="8">
         <v>45703083874</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
+      <c r="A223" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A224">
+      <c r="A224" s="8">
         <v>45703083888</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A225">
+      <c r="A225" s="8">
         <v>45699605281</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A226">
+      <c r="A226" s="8">
         <v>45703793607</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A227">
+      <c r="A227" s="8">
         <v>45698480650</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A228">
+      <c r="A228" s="8">
         <v>45704491326</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A229">
+      <c r="A229" s="8">
         <v>45703020197</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A230">
+      <c r="A230" s="8">
         <v>45693298428</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A231">
+      <c r="A231" s="8">
         <v>45683776687</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A232">
+      <c r="A232" s="8">
         <v>45703601886</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A233">
+      <c r="A233" s="8">
         <v>45703228719</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A234">
+      <c r="A234" s="8">
         <v>45703969703</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A235">
+      <c r="A235" s="8">
         <v>45702029280</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A236">
+      <c r="A236" s="8">
         <v>45699812543</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
+      <c r="A237" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A238">
+      <c r="A238" s="8">
         <v>45704260229</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A239">
+      <c r="A239" s="8">
         <v>45705145877</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A240">
+      <c r="A240" s="8">
         <v>45700833289</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A241">
+      <c r="A241" s="8">
         <v>45702928078</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A242">
+      <c r="A242" s="8">
         <v>45699964115</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A243">
+      <c r="A243" s="8">
         <v>45693810663</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A244">
+      <c r="A244" s="8">
         <v>45683464616</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A245">
+      <c r="A245" s="8">
         <v>45704431164</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
+      <c r="A246" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A247">
+      <c r="A247" s="8">
         <v>45689034640</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A248">
+      <c r="A248" s="8">
         <v>45704788640</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A249">
+      <c r="A249" s="8">
         <v>45685035862</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A250">
+      <c r="A250" s="8">
         <v>45699928819</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A251">
+      <c r="A251" s="8">
         <v>45699881954</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A252">
+      <c r="A252" s="8">
         <v>45690401411</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A253">
+      <c r="A253" s="8">
         <v>45699676334</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A254">
+      <c r="A254" s="8">
         <v>45667678432</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A255">
+      <c r="A255" s="8">
         <v>45701066338</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
+      <c r="A256" s="8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
+      <c r="A257" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A258">
+      <c r="A258" s="8">
         <v>45703080292</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A259">
+      <c r="A259" s="8">
         <v>45700196386</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A260">
+      <c r="A260" s="8">
         <v>45699071106</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A261">
+      <c r="A261" s="8">
         <v>45705172784</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
+      <c r="A262" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A263">
+      <c r="A263" s="8">
         <v>45699552061</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A264">
+      <c r="A264" s="8">
         <v>45700079680</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A265">
+      <c r="A265" s="8">
         <v>45690641525</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A266">
+      <c r="A266" s="8">
         <v>45702928214</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A267">
+      <c r="A267" s="8">
         <v>45698248123</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
+      <c r="A268" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A269">
+      <c r="A269" s="8">
         <v>45693761264</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A270">
+      <c r="A270" s="8">
         <v>45692890232</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A271">
+      <c r="A271" s="8">
         <v>45704676318</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
+      <c r="A272" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
+      <c r="A273" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A274">
+      <c r="A274" s="8">
         <v>45690155264</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A275">
+      <c r="A275" s="8">
         <v>45701550089</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A276">
+      <c r="A276" s="8">
         <v>45697469810</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A277">
+      <c r="A277" s="8">
         <v>45688721304</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
+      <c r="A278" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A279">
+      <c r="A279" s="8">
         <v>45697837141</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A280">
+      <c r="A280" s="8">
         <v>829253080016</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A281">
+      <c r="A281" s="8">
         <v>45693929124</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
+      <c r="A282" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
+      <c r="A283" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
+      <c r="A284" s="8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A285">
+      <c r="A285" s="8">
         <v>45689945453</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A286">
+      <c r="A286" s="8">
         <v>45699493970</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A287">
+      <c r="A287" s="8">
         <v>45699493826</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A288">
+      <c r="A288" s="8">
         <v>45699242485</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A289">
+      <c r="A289" s="8">
         <v>45699242009</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A290">
+      <c r="A290" s="8">
         <v>45699243529</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A291">
+      <c r="A291" s="8">
         <v>45699494110</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A292">
+      <c r="A292" s="8">
         <v>45699242109</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A293">
+      <c r="A293" s="8">
         <v>45699242179</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A294">
+      <c r="A294" s="8">
         <v>45699493940</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A295">
+      <c r="A295" s="8">
         <v>45699242423</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A296">
+      <c r="A296" s="8">
         <v>45699243665</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A297">
+      <c r="A297" s="8">
         <v>45699494496</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A298">
+      <c r="A298" s="8">
         <v>45699493916</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A299">
+      <c r="A299" s="8">
         <v>45699494048</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
+      <c r="A300" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A301">
+      <c r="A301" s="8">
         <v>45704776976</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A302">
+      <c r="A302" s="8">
         <v>45699493978</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A303">
+      <c r="A303" s="8">
         <v>45699244207</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A304">
+      <c r="A304" s="8">
         <v>45699242131</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A305">
+      <c r="A305" s="8">
         <v>45691751803</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A306">
+      <c r="A306" s="8">
         <v>45699493340</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A307">
+      <c r="A307" s="8">
         <v>45699242637</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
+      <c r="A308" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A309">
+      <c r="A309" s="8">
         <v>45702040031</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
+      <c r="A310" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A311">
+      <c r="A311" s="8">
         <v>956730080010</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
+      <c r="A312" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
+      <c r="A313" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
+      <c r="A314" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A315">
+      <c r="A315" s="8">
         <v>45699062690</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A316">
+      <c r="A316" s="8">
         <v>45703433836</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A317">
+      <c r="A317" s="8">
         <v>45691369114</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A318">
+      <c r="A318" s="8">
         <v>45701643928</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A319">
+      <c r="A319" s="8">
         <v>45690285008</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
+      <c r="A320" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
+      <c r="A321" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A322" t="s">
+      <c r="A322" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A323" t="s">
+      <c r="A323" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A324">
+      <c r="A324" s="8">
         <v>957200080019</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A325">
+      <c r="A325" s="8">
         <v>957075880014</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A326">
+      <c r="A326" s="8">
         <v>957196080015</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A327">
+      <c r="A327" s="8">
         <v>45704459557</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A328" t="s">
+      <c r="A328" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A329" t="s">
+      <c r="A329" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A330">
+      <c r="A330" s="8">
         <v>957061410016</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A331" t="s">
+      <c r="A331" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
+      <c r="A332" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A333">
+      <c r="A333" s="8">
         <v>954173470012</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A334">
+      <c r="A334" s="8">
         <v>953398130013</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A335" t="s">
+      <c r="A335" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A336" t="s">
+      <c r="A336" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A337">
+      <c r="A337" s="8">
         <v>952852100017</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A338">
+      <c r="A338" s="8">
         <v>954532130018</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A339" t="s">
+      <c r="A339" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A340">
+      <c r="A340" s="8">
         <v>957075870015</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A341">
+      <c r="A341" s="8">
         <v>957295300017</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A342" t="s">
+      <c r="A342" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
+      <c r="A343" s="8" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
+      <c r="A344" s="8" t="s">
         <v>46</v>
       </c>
     </row>
